--- a/braph2individualconnectome/pipelines/neuroimaging conversion PDFs/Example data NIfTI PDF shape covariation/reference_data/pdf_gmprob/sub-0008_ses-01_GMprob_pdf.xlsx
+++ b/braph2individualconnectome/pipelines/neuroimaging conversion PDFs/Example data NIfTI PDF shape covariation/reference_data/pdf_gmprob/sub-0008_ses-01_GMprob_pdf.xlsx
@@ -1,7 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <fileVersion appName="libxl" rupBuild="4.6.0"/>
   <workbookPr/>
   <bookViews>
     <workbookView activeTab="0"/>
@@ -13300,7 +13299,7 @@
         <v>0</v>
       </c>
       <c r="AD37" s="0">
-        <v>0.071377587437544549</v>
+        <v>0.071377587437544548</v>
       </c>
       <c r="AE37" s="0">
         <v>0</v>
@@ -13713,7 +13712,7 @@
         <v>0</v>
       </c>
       <c r="AU38" s="0">
-        <v>0.037091988130563768</v>
+        <v>0.037091988130563767</v>
       </c>
       <c r="AV38" s="0">
         <v>0.044712720769058759</v>
@@ -13776,7 +13775,7 @@
         <v>0</v>
       </c>
       <c r="BP38" s="0">
-        <v>0.022045855379188691</v>
+        <v>0.02204585537918869</v>
       </c>
       <c r="BQ38" s="0">
         <v>0</v>
@@ -13997,7 +13996,7 @@
         <v>0</v>
       </c>
       <c r="U39" s="0">
-        <v>6.8600111544896763</v>
+        <v>6.8600111544896762</v>
       </c>
       <c r="V39" s="0">
         <v>0</v>
@@ -14171,7 +14170,7 @@
         <v>0</v>
       </c>
       <c r="CA39" s="0">
-        <v>2.105263157894735</v>
+        <v>2.1052631578947349</v>
       </c>
       <c r="CB39" s="0">
         <v>0</v>
@@ -14243,7 +14242,7 @@
         <v>0</v>
       </c>
       <c r="CY39" s="0">
-        <v>0.048626306831996064</v>
+        <v>0.048626306831996063</v>
       </c>
       <c r="CZ39" s="0">
         <v>0.069913773013283553</v>
@@ -14264,7 +14263,7 @@
         <v>0</v>
       </c>
       <c r="DF39" s="0">
-        <v>5.061349693251529</v>
+        <v>5.0613496932515289</v>
       </c>
       <c r="DG39" s="0">
         <v>0</v>
@@ -14799,7 +14798,7 @@
         <v>0</v>
       </c>
       <c r="AU41" s="0">
-        <v>5.8234421364985432</v>
+        <v>5.8234421364985431</v>
       </c>
       <c r="AV41" s="0">
         <v>4.7842611222893137</v>
@@ -15209,7 +15208,7 @@
         <v>0.11055831951354329</v>
       </c>
       <c r="BK42" s="0">
-        <v>5.1308468988254648</v>
+        <v>5.1308468988254647</v>
       </c>
       <c r="BL42" s="0">
         <v>12.30416507451279</v>
@@ -15807,7 +15806,7 @@
         <v>0</v>
       </c>
       <c r="U44" s="0">
-        <v>1.6174010039040701</v>
+        <v>1.61740100390407</v>
       </c>
       <c r="V44" s="0">
         <v>0</v>
@@ -15837,7 +15836,7 @@
         <v>11.134903640256949</v>
       </c>
       <c r="AE44" s="0">
-        <v>0.20491803278688509</v>
+        <v>0.20491803278688508</v>
       </c>
       <c r="AF44" s="0">
         <v>0</v>
@@ -16035,7 +16034,7 @@
         <v>1.8376478108021717</v>
       </c>
       <c r="CS44" s="0">
-        <v>0.044228217602830571</v>
+        <v>0.04422821760283057</v>
       </c>
       <c r="CT44" s="0">
         <v>0</v>
@@ -16071,7 +16070,7 @@
         <v>14.644808743169387</v>
       </c>
       <c r="DE44" s="0">
-        <v>6.4282261962300567</v>
+        <v>6.4282261962300566</v>
       </c>
       <c r="DF44" s="0">
         <v>2.0961145194274011</v>
@@ -16214,7 +16213,7 @@
         <v>15.475828519306766</v>
       </c>
       <c r="AJ45" s="0">
-        <v>6.6563467492260005</v>
+        <v>6.6563467492260004</v>
       </c>
       <c r="AK45" s="0">
         <v>4.1007354579897441</v>
@@ -16418,7 +16417,7 @@
         <v>11.1111111111111</v>
       </c>
       <c r="CZ45" s="0">
-        <v>9.9743649498951204</v>
+        <v>9.9743649498951203</v>
       </c>
       <c r="DA45" s="0">
         <v>0</v>
@@ -16570,7 +16569,7 @@
         <v>0.090538705296514185</v>
       </c>
       <c r="AH46" s="0">
-        <v>12.535680304471923</v>
+        <v>12.535680304471922</v>
       </c>
       <c r="AI46" s="0">
         <v>14.533292794162346</v>
@@ -16750,7 +16749,7 @@
         <v>9.7857709600634664</v>
       </c>
       <c r="CP46" s="0">
-        <v>0.26382060199064617</v>
+        <v>0.26382060199064616</v>
       </c>
       <c r="CQ46" s="0">
         <v>9.2815344603380936</v>
@@ -16974,7 +16973,7 @@
         <v>0.44510385756676768</v>
       </c>
       <c r="AV47" s="0">
-        <v>0.4694835680751196</v>
+        <v>0.46948356807511959</v>
       </c>
       <c r="AW47" s="0">
         <v>0.45748116254036814</v>
@@ -17225,7 +17224,7 @@
         <v>0</v>
       </c>
       <c r="K48" s="0">
-        <v>0.17103762827822106</v>
+        <v>0.17103762827822105</v>
       </c>
       <c r="L48" s="0">
         <v>0.26638252530633966</v>
@@ -17285,7 +17284,7 @@
         <v>0.1427551748750891</v>
       </c>
       <c r="AE48" s="0">
-        <v>16.59836065573769</v>
+        <v>16.598360655737689</v>
       </c>
       <c r="AF48" s="0">
         <v>7.9999999999999929</v>
@@ -17411,13 +17410,13 @@
         <v>0.15263291783261243</v>
       </c>
       <c r="BU48" s="0">
-        <v>2.517873795461608</v>
+        <v>2.5178737954616079</v>
       </c>
       <c r="BV48" s="0">
         <v>12.186732186732176</v>
       </c>
       <c r="BW48" s="0">
-        <v>16.44736842105262</v>
+        <v>16.447368421052619</v>
       </c>
       <c r="BX48" s="0">
         <v>8.708456037021449</v>
@@ -17557,7 +17556,7 @@
     </row>
     <row r="49">
       <c r="A49" s="0">
-        <v>0.18113754377490624</v>
+        <v>0.18113754377490623</v>
       </c>
       <c r="B49" s="0">
         <v>0.47666833918715462</v>
@@ -17653,10 +17652,10 @@
         <v>14.947368421052618</v>
       </c>
       <c r="AG49" s="0">
-        <v>6.6093254866455356</v>
+        <v>6.6093254866455355</v>
       </c>
       <c r="AH49" s="0">
-        <v>1.2607040913415784</v>
+        <v>1.2607040913415783</v>
       </c>
       <c r="AI49" s="0">
         <v>0.8513225904530245</v>
@@ -17797,10 +17796,10 @@
         <v>8.3464566929133781</v>
       </c>
       <c r="CC49" s="0">
-        <v>2.6246719160104966</v>
+        <v>2.6246719160104965</v>
       </c>
       <c r="CD49" s="0">
-        <v>4.1538461538461498</v>
+        <v>4.1538461538461497</v>
       </c>
       <c r="CE49" s="0">
         <v>11.999999999999989</v>
@@ -17919,7 +17918,7 @@
     </row>
     <row r="50">
       <c r="A50" s="0">
-        <v>1.1351286076560792</v>
+        <v>1.1351286076560791</v>
       </c>
       <c r="B50" s="0">
         <v>2.2077270446562949</v>
@@ -17991,7 +17990,7 @@
         <v>0.68220579874928877</v>
       </c>
       <c r="Y50" s="0">
-        <v>0.94339622641509347</v>
+        <v>0.94339622641509346</v>
       </c>
       <c r="Z50" s="0">
         <v>0</v>
@@ -18024,7 +18023,7 @@
         <v>0.15202189115232578</v>
       </c>
       <c r="AJ50" s="0">
-        <v>2.2291021671826608</v>
+        <v>2.2291021671826607</v>
       </c>
       <c r="AK50" s="0">
         <v>0</v>
@@ -18066,7 +18065,7 @@
         <v>0</v>
       </c>
       <c r="AX50" s="0">
-        <v>6.715284108173802</v>
+        <v>6.7152841081738019</v>
       </c>
       <c r="AY50" s="0">
         <v>0</v>
@@ -18287,7 +18286,7 @@
         <v>6.5980933266432462</v>
       </c>
       <c r="C51" s="0">
-        <v>5.5501546619531546</v>
+        <v>5.5501546619531545</v>
       </c>
       <c r="D51" s="0">
         <v>6.9830341775264264</v>
@@ -18299,7 +18298,7 @@
         <v>12.214857536369104</v>
       </c>
       <c r="G51" s="0">
-        <v>9.9759615384615295</v>
+        <v>9.9759615384615294</v>
       </c>
       <c r="H51" s="0">
         <v>5.0560096881622725</v>
@@ -18497,7 +18496,7 @@
         <v>0</v>
       </c>
       <c r="BU51" s="0">
-        <v>16.816910164749754</v>
+        <v>16.816910164749753</v>
       </c>
       <c r="BV51" s="0">
         <v>0.34398034398034366</v>
@@ -18509,7 +18508,7 @@
         <v>11.821623895666796</v>
       </c>
       <c r="BY51" s="0">
-        <v>2.9682274247491614</v>
+        <v>2.9682274247491613</v>
       </c>
       <c r="BZ51" s="0">
         <v>2.8830963665086862</v>
@@ -18626,7 +18625,7 @@
         <v>0</v>
       </c>
       <c r="DL51" s="0">
-        <v>9.1383812010443784</v>
+        <v>9.1383812010443783</v>
       </c>
       <c r="DM51" s="0">
         <v>9.6153846153846079</v>
@@ -18820,7 +18819,7 @@
         <v>4.5101663585951899</v>
       </c>
       <c r="BH52" s="0">
-        <v>4.2336010709504644</v>
+        <v>4.2336010709504643</v>
       </c>
       <c r="BI52" s="0">
         <v>0.010758472296933826</v>
@@ -19011,7 +19010,7 @@
         <v>13.447064726542889</v>
       </c>
       <c r="C53" s="0">
-        <v>13.742819266460439</v>
+        <v>13.742819266460438</v>
       </c>
       <c r="D53" s="0">
         <v>12.621916236374057</v>
@@ -19272,7 +19271,7 @@
         <v>0.2043422733077904</v>
       </c>
       <c r="CL53" s="0">
-        <v>7.9480863963622515</v>
+        <v>7.9480863963622514</v>
       </c>
       <c r="CM53" s="0">
         <v>0</v>
@@ -19756,7 +19755,7 @@
         <v>9.7342192691029812</v>
       </c>
       <c r="J55" s="0">
-        <v>16.190293497026652</v>
+        <v>16.190293497026651</v>
       </c>
       <c r="K55" s="0">
         <v>2.280501710376281</v>
@@ -19786,7 +19785,7 @@
         <v>15.909724157146822</v>
       </c>
       <c r="T55" s="0">
-        <v>5.3677525097316075</v>
+        <v>5.3677525097316074</v>
       </c>
       <c r="U55" s="0">
         <v>0</v>
@@ -20083,7 +20082,7 @@
         <v>0</v>
       </c>
       <c r="DO55" s="0">
-        <v>0.97087378640776601</v>
+        <v>0.970873786407766</v>
       </c>
       <c r="DP55" s="0">
         <v>3.5211267605633774</v>
@@ -20109,7 +20108,7 @@
         <v>0.27545837996040262</v>
       </c>
       <c r="G56" s="0">
-        <v>0.80128205128205055</v>
+        <v>0.80128205128205054</v>
       </c>
       <c r="H56" s="0">
         <v>3.2394792612776238</v>
@@ -21219,7 +21218,7 @@
         <v>0.031152647975077854</v>
       </c>
       <c r="O59" s="0">
-        <v>0.35594225825588261</v>
+        <v>0.3559422582558826</v>
       </c>
       <c r="P59" s="0">
         <v>0</v>
@@ -21228,7 +21227,7 @@
         <v>2.9320987654320958</v>
       </c>
       <c r="R59" s="0">
-        <v>2.0661157024793369</v>
+        <v>2.0661157024793368</v>
       </c>
       <c r="S59" s="0">
         <v>0.19504040122596808</v>
@@ -23017,7 +23016,7 @@
         <v>0</v>
       </c>
       <c r="K64" s="0">
-        <v>0.17103762827822106</v>
+        <v>0.17103762827822105</v>
       </c>
       <c r="L64" s="0">
         <v>0</v>
@@ -23717,7 +23716,7 @@
         <v>2.0195684897139969</v>
       </c>
       <c r="C66" s="0">
-        <v>2.3773751657092333</v>
+        <v>2.3773751657092332</v>
       </c>
       <c r="D66" s="0">
         <v>3.1718711581017924</v>
@@ -24435,7 +24434,7 @@
     </row>
     <row r="68">
       <c r="A68" s="0">
-        <v>2.1253471802922333</v>
+        <v>2.1253471802922332</v>
       </c>
       <c r="B68" s="0">
         <v>9.7340692423482107</v>
@@ -24839,7 +24838,7 @@
         <v>8.1931464174455666</v>
       </c>
       <c r="O69" s="0">
-        <v>3.5198734427526564</v>
+        <v>3.5198734427526563</v>
       </c>
       <c r="P69" s="0">
         <v>4.9308991639652442</v>
@@ -25785,7 +25784,7 @@
         <v>0</v>
       </c>
       <c r="CK71" s="0">
-        <v>0.17879948914431657</v>
+        <v>0.17879948914431656</v>
       </c>
       <c r="CL71" s="0">
         <v>3.2019704433497509</v>
@@ -25886,7 +25885,7 @@
         <v>7.7889143823209688</v>
       </c>
       <c r="B72" s="0">
-        <v>1.4676367285499235</v>
+        <v>1.4676367285499234</v>
       </c>
       <c r="C72" s="0">
         <v>1.4759169244365873</v>
@@ -25934,7 +25933,7 @@
         <v>0.92592592592592504</v>
       </c>
       <c r="R72" s="0">
-        <v>2.0661157024793369</v>
+        <v>2.0661157024793368</v>
       </c>
       <c r="S72" s="0">
         <v>8.4285316244079063</v>
@@ -26254,7 +26253,7 @@
         <v>0.26513477684489595</v>
       </c>
       <c r="D73" s="0">
-        <v>0.22948938611589193</v>
+        <v>0.22948938611589192</v>
       </c>
       <c r="E73" s="0">
         <v>0.28969255209793449</v>
@@ -26374,7 +26373,7 @@
         <v>1.7596566523605135</v>
       </c>
       <c r="AR73" s="0">
-        <v>0.037383177570093421</v>
+        <v>0.03738317757009342</v>
       </c>
       <c r="AS73" s="0">
         <v>0.19841269841269824</v>
@@ -26745,7 +26744,7 @@
         <v>0</v>
       </c>
       <c r="AU74" s="0">
-        <v>0.037091988130563768</v>
+        <v>0.037091988130563767</v>
       </c>
       <c r="AV74" s="0">
         <v>0.15649452269170566</v>
@@ -26913,7 +26912,7 @@
         <v>0</v>
       </c>
       <c r="CY74" s="0">
-        <v>0.048626306831996064</v>
+        <v>0.048626306831996063</v>
       </c>
       <c r="CZ74" s="0">
         <v>0.046609182008855707</v>
@@ -26952,7 +26951,7 @@
         <v>10.263522884882098</v>
       </c>
       <c r="DL74" s="0">
-        <v>8.6161879895561278</v>
+        <v>8.6161879895561277</v>
       </c>
       <c r="DM74" s="0">
         <v>0</v>
@@ -26984,7 +26983,7 @@
         <v>0.0093449210354172429</v>
       </c>
       <c r="F75" s="0">
-        <v>0.068864594990100656</v>
+        <v>0.068864594990100655</v>
       </c>
       <c r="G75" s="0">
         <v>0.080128205128205052</v>
@@ -27107,7 +27106,7 @@
         <v>0.83472454090150172</v>
       </c>
       <c r="AU75" s="0">
-        <v>0.38946587537091954</v>
+        <v>0.38946587537091953</v>
       </c>
       <c r="AV75" s="0">
         <v>1.2519561815336453</v>
@@ -27155,7 +27154,7 @@
         <v>11.487009397457149</v>
       </c>
       <c r="BK75" s="0">
-        <v>3.7708633834741368</v>
+        <v>3.7708633834741367</v>
       </c>
       <c r="BL75" s="0">
         <v>0.45854031333588036</v>
@@ -27568,7 +27567,7 @@
         <v>0</v>
       </c>
       <c r="CB76" s="0">
-        <v>8.5039370078740078</v>
+        <v>8.5039370078740077</v>
       </c>
       <c r="CC76" s="0">
         <v>0.11248593925759272</v>
@@ -27786,7 +27785,7 @@
         <v>0</v>
       </c>
       <c r="AF77" s="0">
-        <v>1.6842105263157881</v>
+        <v>1.684210526315788</v>
       </c>
       <c r="AG77" s="0">
         <v>8.8275237664101329</v>
@@ -28014,10 +28013,10 @@
         <v>0.6061966771441395</v>
       </c>
       <c r="DD77" s="0">
-        <v>0.12750455373406181</v>
+        <v>0.1275045537340618</v>
       </c>
       <c r="DE77" s="0">
-        <v>6.2348960850652429</v>
+        <v>6.2348960850652428</v>
       </c>
       <c r="DF77" s="0">
         <v>0.56237218813905887</v>
@@ -28121,7 +28120,7 @@
         <v>0.18382352941176455</v>
       </c>
       <c r="W78" s="0">
-        <v>0.20512820512820496</v>
+        <v>0.20512820512820495</v>
       </c>
       <c r="X78" s="0">
         <v>12.677657760090948</v>
@@ -28142,7 +28141,7 @@
         <v>9.7872340425531839</v>
       </c>
       <c r="AD78" s="0">
-        <v>0.071377587437544549</v>
+        <v>0.071377587437544548</v>
       </c>
       <c r="AE78" s="0">
         <v>0</v>
@@ -28495,13 +28494,13 @@
         <v>0.13726835964310213</v>
       </c>
       <c r="AA79" s="0">
-        <v>6.1565523306948054</v>
+        <v>6.1565523306948053</v>
       </c>
       <c r="AB79" s="0">
         <v>0.49049662783568315</v>
       </c>
       <c r="AC79" s="0">
-        <v>6.2411347517730445</v>
+        <v>6.2411347517730444</v>
       </c>
       <c r="AD79" s="0">
         <v>0</v>
@@ -28525,7 +28524,7 @@
         <v>10.495356037151693</v>
       </c>
       <c r="AK79" s="0">
-        <v>8.5134833964787085</v>
+        <v>8.5134833964787084</v>
       </c>
       <c r="AL79" s="0">
         <v>1.9733023795705147</v>
@@ -28597,7 +28596,7 @@
         <v>7.9819277108433662</v>
       </c>
       <c r="BI79" s="0">
-        <v>0.032275416890801476</v>
+        <v>0.032275416890801475</v>
       </c>
       <c r="BJ79" s="0">
         <v>0.82918739635157479</v>
@@ -28672,10 +28671,10 @@
         <v>9.6259528452401977</v>
       </c>
       <c r="CH79" s="0">
-        <v>7.1286603948588772</v>
+        <v>7.1286603948588771</v>
       </c>
       <c r="CI79" s="0">
-        <v>9.8502495840266136</v>
+        <v>9.8502495840266135</v>
       </c>
       <c r="CJ79" s="0">
         <v>9.4244149272612177</v>
@@ -28705,7 +28704,7 @@
         <v>6.0722275487376107</v>
       </c>
       <c r="CS79" s="0">
-        <v>0.044228217602830571</v>
+        <v>0.04422821760283057</v>
       </c>
       <c r="CT79" s="0">
         <v>0</v>
@@ -28854,7 +28853,7 @@
         <v>5.1886792452830148</v>
       </c>
       <c r="Z80" s="0">
-        <v>0.75497597803706174</v>
+        <v>0.75497597803706173</v>
       </c>
       <c r="AA80" s="0">
         <v>3.2541776605101114</v>
@@ -28974,7 +28973,7 @@
         <v>4.6584390752650755</v>
       </c>
       <c r="BN80" s="0">
-        <v>1.5523129462899708</v>
+        <v>1.5523129462899707</v>
       </c>
       <c r="BO80" s="0">
         <v>8.2742316784869896</v>
@@ -28998,10 +28997,10 @@
         <v>7.5847062480571896</v>
       </c>
       <c r="BV80" s="0">
-        <v>6.4373464373464318</v>
+        <v>6.4373464373464317</v>
       </c>
       <c r="BW80" s="0">
-        <v>4.0789473684210496</v>
+        <v>4.0789473684210495</v>
       </c>
       <c r="BX80" s="0">
         <v>4.5435422801851031</v>
@@ -29061,7 +29060,7 @@
         <v>2.2304832713754625</v>
       </c>
       <c r="CQ80" s="0">
-        <v>0.032509752925877739</v>
+        <v>0.032509752925877738</v>
       </c>
       <c r="CR80" s="0">
         <v>11.089805049536583</v>
@@ -29133,7 +29132,7 @@
         <v>4.8828124999999956</v>
       </c>
       <c r="DO80" s="0">
-        <v>7.0388349514563045</v>
+        <v>7.0388349514563044</v>
       </c>
       <c r="DP80" s="0">
         <v>3.5211267605633774</v>
@@ -29276,7 +29275,7 @@
         <v>0.59523809523809468</v>
       </c>
       <c r="AT81" s="0">
-        <v>1.6694490818030035</v>
+        <v>1.6694490818030034</v>
       </c>
       <c r="AU81" s="0">
         <v>6.1758160237388671</v>
@@ -29324,7 +29323,7 @@
         <v>1.0220548682087134</v>
       </c>
       <c r="BJ81" s="0">
-        <v>0.022111663902708662</v>
+        <v>0.022111663902708661</v>
       </c>
       <c r="BK81" s="0">
         <v>0.94786729857819829</v>
@@ -29680,7 +29679,7 @@
         <v>2.7356746765249818</v>
       </c>
       <c r="BH82" s="0">
-        <v>0.21753681392235833</v>
+        <v>0.21753681392235832</v>
       </c>
       <c r="BI82" s="0">
         <v>3.3136094674556551</v>
@@ -29803,7 +29802,7 @@
         <v>6.1567164179105101</v>
       </c>
       <c r="CW82" s="0">
-        <v>1.6745540589734425</v>
+        <v>1.6745540589734424</v>
       </c>
       <c r="CX82" s="0">
         <v>7.6701821668265415</v>
@@ -29952,7 +29951,7 @@
         <v>0</v>
       </c>
       <c r="AD83" s="0">
-        <v>5.8529621698786532</v>
+        <v>5.8529621698786531</v>
       </c>
       <c r="AE83" s="0">
         <v>4.7131147540983562</v>
@@ -30006,7 +30005,7 @@
         <v>0.55637982195845648</v>
       </c>
       <c r="AV83" s="0">
-        <v>0.20120724346076444</v>
+        <v>0.20120724346076443</v>
       </c>
       <c r="AW83" s="0">
         <v>0.53821313240043012</v>
@@ -30030,7 +30029,7 @@
         <v>0</v>
       </c>
       <c r="BD83" s="0">
-        <v>0.020554984583761545</v>
+        <v>0.020554984583761544</v>
       </c>
       <c r="BE83" s="0">
         <v>3.9381153305203904</v>
@@ -30063,7 +30062,7 @@
         <v>0.031046258925799413</v>
       </c>
       <c r="BO83" s="0">
-        <v>0.30395136778115473</v>
+        <v>0.30395136778115472</v>
       </c>
       <c r="BP83" s="0">
         <v>0</v>
@@ -30183,7 +30182,7 @@
         <v>0</v>
       </c>
       <c r="DC83" s="0">
-        <v>2.8513695554557677</v>
+        <v>2.8513695554557676</v>
       </c>
       <c r="DD83" s="0">
         <v>7.1766848816029079</v>
@@ -30287,7 +30286,7 @@
         <v>0</v>
       </c>
       <c r="U84" s="0">
-        <v>1.6174010039040701</v>
+        <v>1.61740100390407</v>
       </c>
       <c r="V84" s="0">
         <v>0</v>
@@ -30356,7 +30355,7 @@
         <v>0</v>
       </c>
       <c r="AR84" s="0">
-        <v>0.037383177570093421</v>
+        <v>0.03738317757009342</v>
       </c>
       <c r="AS84" s="0">
         <v>0</v>
@@ -30533,7 +30532,7 @@
         <v>6.3758389261744917</v>
       </c>
       <c r="CY84" s="0">
-        <v>0.048626306831996064</v>
+        <v>0.048626306831996063</v>
       </c>
       <c r="CZ84" s="0">
         <v>0</v>
@@ -30554,7 +30553,7 @@
         <v>0</v>
       </c>
       <c r="DF84" s="0">
-        <v>1.8404907975460108</v>
+        <v>1.8404907975460107</v>
       </c>
       <c r="DG84" s="0">
         <v>0</v>
@@ -30661,7 +30660,7 @@
         <v>0</v>
       </c>
       <c r="Y85" s="0">
-        <v>0.94339622641509347</v>
+        <v>0.94339622641509346</v>
       </c>
       <c r="Z85" s="0">
         <v>6.6575154426904533</v>
@@ -31191,7 +31190,7 @@
         <v>0</v>
       </c>
       <c r="CC86" s="0">
-        <v>0.07499062617172847</v>
+        <v>0.074990626171728469</v>
       </c>
       <c r="CD86" s="0">
         <v>0</v>
@@ -31415,7 +31414,7 @@
         <v>0</v>
       </c>
       <c r="AI87" s="0">
-        <v>4.9255092733353561</v>
+        <v>4.925509273335356</v>
       </c>
       <c r="AJ87" s="0">
         <v>0</v>
@@ -31535,7 +31534,7 @@
         <v>0</v>
       </c>
       <c r="BW87" s="0">
-        <v>0.043859649122806981</v>
+        <v>0.04385964912280698</v>
       </c>
       <c r="BX87" s="0">
         <v>0</v>
@@ -32124,10 +32123,10 @@
         <v>0</v>
       </c>
       <c r="AD89" s="0">
-        <v>0.071377587437544549</v>
+        <v>0.071377587437544548</v>
       </c>
       <c r="AE89" s="0">
-        <v>0.20491803278688509</v>
+        <v>0.20491803278688508</v>
       </c>
       <c r="AF89" s="0">
         <v>0</v>
@@ -32711,7 +32710,7 @@
         <v>0</v>
       </c>
       <c r="DA90" s="0">
-        <v>0.36023054755043194</v>
+        <v>0.36023054755043193</v>
       </c>
       <c r="DB90" s="0">
         <v>3.4482758620689622</v>
